--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing-zeiten.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing-zeiten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:21:25+00:00</t>
+    <t>2026-05-13T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing-zeiten.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing-zeiten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:40:49+00:00</t>
+    <t>2026-05-15T11:09:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing-zeiten.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing-zeiten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T11:09:11+00:00</t>
+    <t>2026-05-22T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing-zeiten.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing-zeiten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T12:28:16+00:00</t>
+    <t>2026-05-27T13:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing-zeiten.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing-zeiten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:46:49+00:00</t>
+    <t>2026-05-28T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
